--- a/data/credit_bond_all_2026-09-18.xlsx
+++ b/data/credit_bond_all_2026-09-18.xlsx
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V18" s="4" t="n">
         <v>1.0</v>
@@ -5130,7 +5130,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26南航集SCP005</t>
+          <t>26中铁四局SCP003</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5140,64 +5140,64 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>012682303.IB</t>
+          <t>012682305.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>0.27Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.25 ~ 1.55</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>19.0</v>
+        <v>16.85</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26南航集SCP003</t>
+          <t>26中铁四局SCP001</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>69D</t>
+          <t>98D</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.4800</t>
+          <t>1.5000</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>1.5100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>中国南方航空集团有限公司</t>
+          <t>中铁四局集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 45.40</t>
+          <t>C- 13.62</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5221,19 +5221,19 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.18</v>
+        <v>3.24</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>11.0</v>
+        <v>1.59</v>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.46%~1.50%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -5244,17 +5244,17 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行拟募集金额为24亿元，发行人计划将用于偿还存量有息债务。</t>
+          <t>本期发行金额5亿元,募集资金拟用于发行人及下属子公司偿还有息债务、补充营运资金。</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中国建设银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>中国南方航空集团有限公司2026年度第五期超短期融资券</t>
+          <t>中铁四局集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5285,14 +5285,10 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
-        </is>
-      </c>
-      <c r="AK22" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
           <t>2026-09-21</t>
@@ -5315,27 +5311,27 @@
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5363,14 +5359,12 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="AZ22" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ22" s="3"/>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26中铁四局SCP003</t>
+          <t>26金隅冀东CP001</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5380,49 +5374,49 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>012682305.IB</t>
+          <t>042680321.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>0.27Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.45 ~ 1.70</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>16.85</v>
+        <v>32.02</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26中铁四局SCP001</t>
+          <t>24冀东02</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>98D</t>
+          <t>1.01Y+2.00Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.5000</t>
+          <t>1.5516</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -5432,12 +5426,12 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>中铁四局集团有限公司</t>
+          <t>金隅冀东水泥集团股份有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C- 13.62</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5457,23 +5451,21 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="V23" s="4" t="n">
-        <v>1.59</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.57%~1.61%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5484,28 +5476,28 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额5亿元,募集资金拟用于发行人及下属子公司偿还有息债务、补充营运资金。</t>
+          <t>本期发行金隅冀东水泥集团股份有限公司2026年度第一期短期融资券，发行金额10亿元，募集资金拟用于偿还发行人到期兑付的公司债本金和金融机构借款，拟偿还的有息债务中不涉及政府性债务。</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,兴业银行股份有限公司</t>
+          <t>招商银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG23" s="3" t="inlineStr">
@@ -5515,7 +5507,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>中铁四局集团有限公司2026年度第三期超短期融资券</t>
+          <t>金隅冀东水泥集团股份有限公司2026年度第一期短期融资券</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5525,25 +5517,25 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2027-09-21</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="AM23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -5556,22 +5548,22 @@
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5604,74 +5596,74 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26金隅冀东CP001</t>
+          <t>26高投K1</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>09-18 18:00</t>
+          <t>09-18 19:00</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>042680321.IB</t>
+          <t>525017.SZ</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.45 ~ 1.70</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>32.02</v>
+        <v>36.41</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>24冀东02</t>
+          <t>26高新投创MTN001(科创债)</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>1.01Y+2.00Y</t>
+          <t>2.34Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.5516</t>
+          <t>1.7496</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>金隅冀东水泥集团股份有限公司</t>
+          <t>深圳市高新投创业投资有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C- 22.00</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5681,7 +5673,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>09-18 09:00</t>
+          <t>09-18 15:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -5695,44 +5687,52 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.8</v>
+        <v>3.47</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.61%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>河北省-唐山市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期发行金隅冀东水泥集团股份有限公司2026年度第一期短期融资券，发行金额10亿元，募集资金拟用于偿还发行人到期兑付的公司债本金和金融机构借款，拟偿还的有息债务中不涉及政府性债务。</t>
+          <t>本期债券募集资金3亿元扣除发行费用后,拟全部用于科技创新领域。投向科技创新领域的具体方式为:通过基金出资对科技创新企业进行权益出资,或对发行前十二个月内的科技创新领域相关投资支出进行置换。</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,交通银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD24" s="3"/>
+          <t>国信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr">
+        <is>
+          <t>深圳市高新投融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5742,12 +5742,12 @@
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>金隅冀东水泥集团股份有限公司2026年度第一期短期融资券</t>
+          <t>深圳市高新投创业投资有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5757,18 +5757,18 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2027-09-21</t>
+          <t>2029-09-21</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t/>
         </is>
       </c>
       <c r="AM24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AN24" s="3" t="inlineStr">
@@ -5778,32 +5778,28 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP24" s="3"/>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5813,7 +5809,7 @@
       </c>
       <c r="AV24" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW24" s="3" t="inlineStr">
@@ -5836,74 +5832,70 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26高投K1</t>
+          <t>26南山K3</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>09-18 19:00</t>
+          <t>09-18 00:00</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>525017.SZ</t>
+          <t>284027.SH</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>1.40 ~ 2.00</t>
-        </is>
-      </c>
+        <v>15.0</v>
+      </c>
+      <c r="G25" s="3"/>
       <c r="H25" s="4" t="n">
-        <v>1.63</v>
+        <v>2.8</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>36.41</v>
+        <v>153.41</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26高新投创MTN001(科创债)</t>
+          <t>26南山K2</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>2.34Y</t>
+          <t>1.58Y+1.00Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.7496</t>
+          <t>2.7086</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.7500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>深圳市高新投创业投资有限公司</t>
+          <t>南山集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C- 22.00</t>
+          <t>C+ 33.04</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5913,7 +5905,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>09-18 15:00</t>
+          <t>09-18 00:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5927,22 +5919,22 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.47</v>
+        <v>1.0</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>3.41%~3.51%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
@@ -5952,24 +5944,20 @@
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>山东省-烟台市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金3亿元扣除发行费用后,拟全部用于科技创新领域。投向科技创新领域的具体方式为:通过基金出资对科技创新企业进行权益出资,或对发行前十二个月内的科技创新领域相关投资支出进行置换。</t>
+          <t>本期债券的募集资金拟全部用于偿还到期债务</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD25" s="3" t="inlineStr">
-        <is>
-          <t>深圳市高新投融资担保有限公司</t>
-        </is>
-      </c>
+          <t>金圆统一证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -5977,22 +5965,22 @@
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>深圳市高新投创业投资有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>南山集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
@@ -6008,7 +5996,7 @@
       </c>
       <c r="AM25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AN25" s="3" t="inlineStr">
@@ -6018,43 +6006,47 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP25" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>常用有色金属</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>工业金属</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2028-09-21</t>
         </is>
       </c>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW25" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX25" s="3" t="inlineStr">
@@ -6072,104 +6064,110 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26南山K3</t>
+          <t>26南航集SCP005</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>09-18 00:00</t>
+          <t>09-18 18:00</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>284027.SH</t>
+          <t>012682303.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>2+1</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>15.0</v>
+        <v>24.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="G26" s="3"/>
+        <v>24.0</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>1.25 ~ 1.55</t>
+        </is>
+      </c>
       <c r="H26" s="4" t="n">
-        <v>2.8</v>
+        <v>1.37</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>153.41</v>
+        <v>19.0</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>26南航集SCP003</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>69D</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>1.4800</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>中国南方航空集团有限公司</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>B- 45.40</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>09-18 09:00</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>26南山K2</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>1.58Y+1.00Y</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>2.7086</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>南山集团有限公司</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t>C+ 33.04</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t>09-18 00:00</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="V26" s="3"/>
+        <v>2.175</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>11.0</v>
+      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>3.41%~3.51%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -6177,108 +6175,108 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>山东省-烟台市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金拟全部用于偿还到期债务</t>
+          <t>本期超短期融资券发行拟募集金额为24亿元，发行人计划将用于偿还存量有息债务。</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>金圆统一证券有限公司</t>
+          <t>兴业银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>南山集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
+          <t>中国南方航空集团有限公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2029-09-21</t>
-        </is>
-      </c>
-      <c r="AK26" s="3"/>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="AK26" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL26" s="3" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>航空</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>航空</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>航空运输</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="AO26" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ26" s="3" t="inlineStr">
-        <is>
-          <t>金属和非金属矿产</t>
-        </is>
-      </c>
-      <c r="AR26" s="3" t="inlineStr">
-        <is>
-          <t>有色</t>
-        </is>
-      </c>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>常用有色金属</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>工业金属</t>
-        </is>
-      </c>
-      <c r="AU26" s="3" t="inlineStr">
-        <is>
-          <t>2028-09-21</t>
-        </is>
-      </c>
       <c r="AV26" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -6286,7 +6284,7 @@
       </c>
       <c r="AW26" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX26" s="3" t="inlineStr">
@@ -6299,7 +6297,9 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="AZ26" s="3"/>
+      <c r="AZ26" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-18.xlsx
+++ b/data/credit_bond_all_2026-09-18.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-23" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-24" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>B- 40.00</t>
+          <t>B 52.50</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.11</t>
+          <t>C+ 33.15</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>B- 43.76</t>
+          <t>B- 43.51</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>B- 45.85</t>
+          <t>B- 40.79</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>B- 40.86</t>
+          <t>B- 45.71</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C 29.54</t>
+          <t>C 29.64</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.11</t>
+          <t>C+ 33.15</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C- 11.53</t>
+          <t>C- 13.22</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>B- 38.27</t>
+          <t>B- 36.23</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C- 15.91</t>
+          <t>C- 17.06</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 35.39</t>
+          <t>B- 35.10</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B- 36.04</t>
+          <t>B- 37.68</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 36.24</t>
+          <t>B- 38.95</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5315,7 +5315,7 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM22" s="3" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>B- 49.17</t>
+          <t>B 54.46</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5547,7 +5547,7 @@
       <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM23" s="3" t="inlineStr">
@@ -6019,7 +6019,7 @@
       <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM25" s="3" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>D 3.66</t>
+          <t>C- 17.41</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="AL26" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM26" s="3" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 24.64</t>
+          <t>C 25.08</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6483,7 +6483,7 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>B- 46.03</t>
+          <t>B- 46.75</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AL28" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM28" s="3" t="inlineStr">
@@ -6947,7 +6947,7 @@
       <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
@@ -7175,7 +7175,7 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM30" s="3" t="inlineStr">
@@ -7403,7 +7403,7 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM31" s="3" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>B- 38.17</t>
+          <t>B- 36.25</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7635,7 +7635,7 @@
       <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM32" s="3" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.60</t>
+          <t>C- 11.12</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7871,7 +7871,7 @@
       <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM33" s="3" t="inlineStr">
@@ -8107,7 +8107,7 @@
       <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM34" s="3" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 22.21</t>
+          <t>C- 23.31</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8335,7 +8335,7 @@
       <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM35" s="3" t="inlineStr">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7200/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C 27.78</t>
+          <t>C+ 30.55</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8661,7 +8661,9 @@
       <c r="E37" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F37" s="3"/>
+      <c r="F37" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
           <t>1.40 ~ 2.40</t>
@@ -8705,7 +8707,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>B+ 58.93</t>
+          <t>B 54.04</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8728,7 +8730,9 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="U37" s="3"/>
+      <c r="U37" s="4" t="n">
+        <v>3.48</v>
+      </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
@@ -8917,7 +8921,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>B- 36.24</t>
+          <t>B- 38.95</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -9151,7 +9155,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 16.58</t>
+          <t>C- 17.97</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9243,7 +9247,7 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM39" s="3" t="inlineStr">
@@ -9377,7 +9381,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>B- 37.29</t>
+          <t>B- 44.31</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9847,7 +9851,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C 27.27</t>
+          <t>C 28.18</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -10175,7 +10179,7 @@
       <c r="AK43" s="3"/>
       <c r="AL43" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM43" s="3" t="inlineStr">
@@ -10545,7 +10549,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.86</t>
+          <t>B- 35.52</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10773,7 +10777,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>A- 64.60</t>
+          <t>A- 68.49</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10995,7 +10999,7 @@
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>S 91.48</t>
+          <t>S 92.88</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -11221,7 +11225,7 @@
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>B- 35.83</t>
+          <t>B- 41.67</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11455,7 +11459,7 @@
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>B+ 58.09</t>
+          <t>B+ 58.75</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -11681,7 +11685,7 @@
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>C- 18.63</t>
+          <t>C- 18.28</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -12009,7 +12013,7 @@
       <c r="AK51" s="3"/>
       <c r="AL51" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM51" s="3" t="inlineStr">
@@ -12149,7 +12153,7 @@
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>B- 40.80</t>
+          <t>B- 44.67</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -12385,7 +12389,7 @@
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.94</t>
+          <t>C+ 33.33</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12625,7 +12629,7 @@
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.94</t>
+          <t>C+ 33.33</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -13101,7 +13105,7 @@
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>B- 39.90</t>
+          <t>B- 40.05</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -13333,7 +13337,7 @@
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>B- 37.29</t>
+          <t>B- 44.31</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13429,7 +13433,7 @@
       <c r="AK57" s="3"/>
       <c r="AL57" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM57" s="3" t="inlineStr">
@@ -13569,7 +13573,7 @@
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>B- 37.41</t>
+          <t>B- 39.39</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13797,7 +13801,7 @@
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>A+ 84.46</t>
+          <t>S- 87.46</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -14127,7 +14131,7 @@
       </c>
       <c r="AL60" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM60" s="3" t="inlineStr">
@@ -14495,7 +14499,7 @@
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>B- 48.90</t>
+          <t>B 53.40</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-18.xlsx
+++ b/data/credit_bond_all_2026-09-18.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
@@ -5156,7 +5156,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26象集04</t>
+          <t>26智航01</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5166,49 +5166,49 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>246117.SH</t>
+          <t>520472.SZ</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>7.5</v>
+        <v>6.0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>15.0</v>
+        <v>6.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.50</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>79.3</v>
+        <v>50.41</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26象屿MTN005</t>
+          <t>25智航01</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>2.28Y+2.00Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>2.2887</t>
+          <t>1.7639</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>厦门象屿集团有限公司</t>
+          <t>桐乡市智航商业管理集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 38.95</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5247,41 +5247,45 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>2.40%~2.50%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟不超过15.00亿元用于偿还到期公司债券本金或置换偿还公司债券本金的自有资金[23 象屿G4,23 象屿G5]</t>
+          <t>本期债券的募集资金扣除发行费用后，拟用于偿还公司有息债务。</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,华福证券股份有限公司,广发证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,中国银河证券股份有限公司,平安证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD22" s="3"/>
+          <t>浙商证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr">
+        <is>
+          <t>中国投融资担保股份有限公司</t>
+        </is>
+      </c>
       <c r="AE22" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -5294,28 +5298,32 @@
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>厦门象屿集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种二)</t>
+          <t>桐乡市智航商业管理集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2031-09-22</t>
-        </is>
-      </c>
-      <c r="AK22" s="3"/>
+          <t>2029-09-22</t>
+        </is>
+      </c>
+      <c r="AK22" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t/>
         </is>
       </c>
       <c r="AM22" s="3" t="inlineStr">
@@ -5335,27 +5343,27 @@
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>房地产服务</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>其他房地产服务</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5365,7 +5373,7 @@
       </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW22" s="3" t="inlineStr">
@@ -5388,7 +5396,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26HDGJK2</t>
+          <t>26如皋02</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5398,64 +5406,64 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>246107.SH</t>
+          <t>284074.SH</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>2.20 ~ 3.20</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.69</v>
+        <v>2.65</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>28.3</v>
+        <v>96.8</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26华电股MTN002</t>
+          <t>25如皋04</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>3.48Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.7189</t>
+          <t>1.7708</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>1.7300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>华电国际电力股份有限公司</t>
+          <t>如皋市城市产业发展集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>B 54.46</t>
+          <t>C- 13.56</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5479,38 +5487,34 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>3.77</v>
+        <v>4.82</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="inlineStr">
-        <is>
-          <t>1.67%~1.77%</t>
-        </is>
-      </c>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X23" s="3"/>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途。</t>
+          <t>本期债券的募集资金将用于偿还回售公司债券本金[23如皋01]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,广发证券股份有限公司,招商证券股份有限公司,兴业证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
@@ -5521,7 +5525,7 @@
       </c>
       <c r="AF23" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG23" s="3" t="inlineStr">
@@ -5531,17 +5535,17 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>华电国际电力股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)</t>
+          <t>如皋市城市产业发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2031-09-22</t>
+          <t>2036-09-22</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
@@ -5562,32 +5566,32 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5620,7 +5624,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26智航01</t>
+          <t>26如皋01</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5630,49 +5634,49 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>520472.SZ</t>
+          <t>284073.SH</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>50.41</v>
+        <v>49.3</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>25智航01</t>
+          <t>25如皋04</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2.28Y+2.00Y</t>
+          <t>3.48Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.7639</t>
+          <t>1.7708</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -5682,12 +5686,12 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>桐乡市智航商业管理集团有限公司</t>
+          <t>如皋市城市产业发展集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 13.56</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5711,19 +5715,15 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t>1.88%~1.98%</t>
-        </is>
-      </c>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X24" s="3"/>
       <c r="Y24" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -5732,24 +5732,20 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除发行费用后，拟用于偿还公司有息债务。</t>
+          <t>本期债券的募集资金将用于偿还回售公司债券本金[23如皋01]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD24" s="3" t="inlineStr">
-        <is>
-          <t>中国投融资担保股份有限公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -5762,12 +5758,12 @@
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>桐乡市智航商业管理集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>如皋市城市产业发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5777,67 +5773,63 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2029-09-22</t>
-        </is>
-      </c>
-      <c r="AK24" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-22</t>
+        </is>
+      </c>
+      <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM24" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AO24" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ24" s="3" t="inlineStr">
-        <is>
-          <t>房地产</t>
-        </is>
-      </c>
-      <c r="AR24" s="3" t="inlineStr">
-        <is>
-          <t>房地产服务</t>
-        </is>
-      </c>
-      <c r="AS24" s="3" t="inlineStr">
-        <is>
-          <t>其他房地产服务</t>
-        </is>
-      </c>
-      <c r="AT24" s="3" t="inlineStr">
-        <is>
-          <t>专业工程</t>
-        </is>
-      </c>
-      <c r="AU24" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV24" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW24" s="3" t="inlineStr">
@@ -5860,7 +5852,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26连工01</t>
+          <t>26皖交02</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5870,7 +5862,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>284016.SH</t>
+          <t>246131.SH</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -5879,55 +5871,55 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.5</v>
+        <v>20.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.5</v>
+        <v>20.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.04</v>
+        <v>1.69</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>63.3</v>
+        <v>28.3</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>24连工03</t>
+          <t>24皖交控MTN002</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>212D</t>
+          <t>4.44Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.7683</t>
+          <t>1.7081</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7200/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>连云港市工业投资集团有限公司</t>
+          <t>安徽省交通控股集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C- 13.40</t>
+          <t>C+ 30.55</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5947,42 +5939,38 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.31</v>
+        <v>3.5</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t>1.97%~2.07%</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X25" s="3"/>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>江苏省-连云港市</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,将全部用于偿还到期债务[26连云工投SCP001]</t>
+          <t>本期债券募集资金不超过20亿元(含20亿元)，发行人拟用于偿还上表所列示的公司债券本金[23皖交05]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
@@ -6003,63 +5991,67 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>连云港市工业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>安徽省交通控股集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2031-09-22</t>
-        </is>
-      </c>
-      <c r="AK25" s="3"/>
+          <t>2031-09-21</t>
+        </is>
+      </c>
+      <c r="AK25" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AM25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AN25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>化学原料</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -6092,7 +6084,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26上发01</t>
+          <t>26柯开02</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6102,7 +6094,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>284045.SH</t>
+          <t>284077.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -6111,55 +6103,55 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>42.41</v>
+        <v>41.41</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>23上发Y1</t>
+          <t>26柯开01</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>91D+N</t>
+          <t>2.77Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.5266</t>
+          <t>1.6986</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/1.5200</t>
+          <t>--/1.7000</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>杭州上城区城市建设发展集团有限公司</t>
+          <t>绍兴市柯桥区开发经营集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 17.41</t>
+          <t>B 54.04</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6179,16 +6171,16 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.83</v>
+        <v>3.48</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X26" s="3"/>
@@ -6200,17 +6192,17 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还发行人存量公司债券[23上发01]</t>
+          <t>本期债券募集资金5亿元,拟全部用于偿还到期公司债券本金。[23柯开02]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
@@ -6231,7 +6223,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>杭州上城区城市建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>绍兴市柯桥区开发经营集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6241,17 +6233,17 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2029-09-22</t>
+          <t>2029-09-23</t>
         </is>
       </c>
       <c r="AK26" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t/>
         </is>
       </c>
       <c r="AM26" s="3" t="inlineStr">
@@ -6261,7 +6253,7 @@
       </c>
       <c r="AN26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AO26" s="3" t="inlineStr">
@@ -6271,27 +6263,15 @@
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ26" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR26" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3"/>
+      <c r="AR26" s="3"/>
+      <c r="AS26" s="3"/>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6324,7 +6304,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26平诚04</t>
+          <t>26维投02</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6334,19 +6314,19 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>284050.SH</t>
+          <t>284067.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.65</v>
+        <v>4.9</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.65</v>
+        <v>4.9</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -6354,29 +6334,29 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>32.3</v>
+        <v>57.3</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>24平诚03</t>
+          <t>26维投01</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>3.19Y</t>
+          <t>4.56Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.8259</t>
+          <t>1.8078</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -6386,12 +6366,12 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>平阳县国诚控股有限公司</t>
+          <t>扬州维投控股集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C 25.08</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6415,17 +6395,17 @@
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.22</v>
+        <v>2.7551</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.98%~2.08%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -6436,17 +6416,17 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>江苏省-扬州市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,拟用于置换回售、偿还到期公司债券本金[23平诚02,21平阳02]</t>
+          <t>本期公司债券募集资金4.90亿元拟用于偿还到期的公司债券本金[23维扬01]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,东吴证券股份有限公司,兴业证券股份有限公司,浙商证券股份有限公司,财通证券股份有限公司</t>
+          <t>国金证券股份有限公司,东莞证券股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
@@ -6467,7 +6447,7 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>平阳县国诚控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>扬州维投控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6503,32 +6483,32 @@
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
         <is>
-          <t>2029-09-22</t>
+          <t/>
         </is>
       </c>
       <c r="AV27" s="3" t="inlineStr">
@@ -6538,7 +6518,7 @@
       </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX27" s="3" t="inlineStr">
@@ -6556,7 +6536,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26横琴05</t>
+          <t>26平诚04</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6566,64 +6546,64 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>284069.SH</t>
+          <t>284050.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>7.0</v>
+        <v>5.65</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7.0</v>
+        <v>5.65</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.10</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>52.41</v>
+        <v>32.3</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>24横琴02</t>
+          <t>24平诚03</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>3.10Y</t>
+          <t>3.19Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.8525</t>
+          <t>1.8259</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>1.8900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>珠海大横琴集团有限公司</t>
+          <t>平阳县国诚控股有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>B- 46.75</t>
+          <t>C 25.08</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6647,34 +6627,38 @@
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.51</v>
+        <v>4.22</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X28" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>1.77%~1.87%</t>
+        </is>
+      </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务。</t>
+          <t>本期债券募集资金在扣除发行费用后,拟用于置换回售、偿还到期公司债券本金[23平诚02,21平阳02]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司</t>
+          <t>天风证券股份有限公司,东吴证券股份有限公司,兴业证券股份有限公司,浙商证券股份有限公司,财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6695,7 +6679,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>珠海大横琴集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>平阳县国诚控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6705,64 +6689,60 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
+          <t>2031-09-22</t>
+        </is>
+      </c>
+      <c r="AK28" s="3"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
           <t>2029-09-22</t>
         </is>
       </c>
-      <c r="AK28" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
-      <c r="AL28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AM28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AO28" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ28" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR28" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS28" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT28" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU28" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV28" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -6770,7 +6750,7 @@
       </c>
       <c r="AW28" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX28" s="3" t="inlineStr">
@@ -6788,7 +6768,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26维投02</t>
+          <t>26上发01</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6798,49 +6778,49 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>284067.SH</t>
+          <t>284045.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.9</v>
+        <v>15.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.9</v>
+        <v>15.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.98</v>
+        <v>1.69</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>57.3</v>
+        <v>42.41</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26维投01</t>
+          <t>23上发Y1</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>4.56Y</t>
+          <t>91D+N</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.8078</t>
+          <t>1.5266</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6850,12 +6830,12 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>扬州维投控股集团有限公司</t>
+          <t>杭州上城区城市建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 17.41</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6879,38 +6859,34 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.7551</v>
+        <v>3.83</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t>1.98%~2.08%</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X29" s="3"/>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>江苏省-扬州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金4.90亿元拟用于偿还到期的公司债券本金[23维扬01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还发行人存量公司债券[23上发01]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,东莞证券股份有限公司</t>
+          <t>东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6931,7 +6907,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>扬州维投控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>杭州上城区城市建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6941,10 +6917,14 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-09-22</t>
-        </is>
-      </c>
-      <c r="AK29" s="3"/>
+          <t>2029-09-22</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL29" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -6967,7 +6947,7 @@
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
@@ -6987,7 +6967,7 @@
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -7020,7 +7000,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26如皋02</t>
+          <t>26穗城01</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -7030,49 +7010,49 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>284074.SH</t>
+          <t>283999.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 3.20</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.65</v>
+        <v>1.78</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>96.8</v>
+        <v>37.3</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>25如皋04</t>
+          <t>25穗城03</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>3.48Y</t>
+          <t>3.50Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.7708</t>
+          <t>1.7420</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -7082,12 +7062,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>如皋市城市产业发展集团有限公司</t>
+          <t>广州市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 13.56</t>
+          <t>B- 36.25</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7111,34 +7091,38 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>4.82</v>
+        <v>3.99</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X30" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>1.89%~1.99%</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将用于偿还回售公司债券本金[23如皋01]</t>
+          <t>本期债券发行规模不超过20亿元(含20亿元),本期债券募集资金扣除发行费用后用于偿还公司有息负债</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>广发证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -7159,7 +7143,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>如皋市城市产业发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>广州市城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7169,7 +7153,7 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2036-09-22</t>
+          <t>2031-09-22</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
@@ -7180,7 +7164,7 @@
       </c>
       <c r="AM30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AN30" s="3" t="inlineStr">
@@ -7195,27 +7179,27 @@
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7248,7 +7232,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26如皋01</t>
+          <t>26湖产03</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7258,49 +7242,49 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>284073.SH</t>
+          <t>284117.SH</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.0</v>
+        <v>7.1</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.0</v>
+        <v>7.1</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>49.3</v>
+        <v>40.3</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>25如皋04</t>
+          <t>24湖产05</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>3.48Y</t>
+          <t>2.87Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.7708</t>
+          <t>1.8466</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -7310,12 +7294,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>如皋市城市产业发展集团有限公司</t>
+          <t>湖州市产业投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C- 13.56</t>
+          <t>C- 23.31</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7339,34 +7323,34 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3.68</v>
+        <v>2.86</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X31" s="3"/>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将用于偿还回售公司债券本金[23如皋01]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券本金[23湖产K2]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>德邦证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
@@ -7387,7 +7371,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>如皋市城市产业发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+          <t>湖州市产业投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7418,37 +7402,37 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-22</t>
         </is>
       </c>
       <c r="AV31" s="3" t="inlineStr">
@@ -7458,7 +7442,7 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
@@ -7476,7 +7460,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26穗城01</t>
+          <t>26绵兴01</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7486,7 +7470,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>283999.SH</t>
+          <t>284079.SH</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -7495,55 +7479,55 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>20.0</v>
+        <v>1.5</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>20.0</v>
+        <v>1.5</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.80 ~ 3.00</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>37.3</v>
+        <v>66.3</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>25穗城03</t>
+          <t>25绵兴03</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>3.50Y</t>
+          <t>4.27Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.7420</t>
+          <t>2.0005</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>1.7400/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>广州市城市建设投资集团有限公司</t>
+          <t>绵阳新兴投资控股有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>B- 36.25</t>
+          <t>C- 11.12</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7567,41 +7551,45 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.99</v>
+        <v>6.43</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.89%~1.99%</t>
+          <t>2.64%~2.74%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>四川省-绵阳市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过20亿元(含20亿元),本期债券募集资金扣除发行费用后用于偿还公司有息负债</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将用于偿还境内公司债券本金[23绵兴03]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD32" s="3"/>
+          <t>光大证券股份有限公司,申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr">
+        <is>
+          <t>四川发展融资担保股份有限公司</t>
+        </is>
+      </c>
       <c r="AE32" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -7619,7 +7607,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>广州市城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>绵阳新兴投资控股有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7655,29 +7643,29 @@
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR32" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
       <c r="AU32" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7685,7 +7673,7 @@
       </c>
       <c r="AV32" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW32" s="3" t="inlineStr">
@@ -7708,7 +7696,7 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26绵兴01</t>
+          <t>26广城08</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7718,49 +7706,49 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>284079.SH</t>
+          <t>246100.SH</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+2</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.5</v>
+        <v>21.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 3.00</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>66.3</v>
+        <v>41.46</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>25绵兴03</t>
+          <t>26广城06</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>4.27Y</t>
+          <t>4.86Y+2.00Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>2.0005</t>
+          <t>2.0326</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -7770,12 +7758,12 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>绵阳新兴投资控股有限公司</t>
+          <t>广州市城市建设开发有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C- 11.12</t>
+          <t>B- 44.31</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7785,7 +7773,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>09-18 15:00</t>
+          <t>09-18 16:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7799,43 +7787,43 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>6.43</v>
+        <v>2.73</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t>2.64%~2.74%</t>
-        </is>
-      </c>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X33" s="3"/>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z33" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>四川省-绵阳市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将用于偿还境内公司债券本金[23绵兴03]</t>
+          <t>本期债券发行规模为不超过21亿元(含21亿元),募集资金扣除发行费用后,拟全部用于偿还到期公司债券[21穗建05,23穗建07]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,申万宏源证券有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3" t="inlineStr">
         <is>
-          <t>四川发展融资担保股份有限公司</t>
+          <t>广州越秀集团股份有限公司</t>
         </is>
       </c>
       <c r="AE33" s="3" t="inlineStr">
@@ -7855,17 +7843,17 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>绵阳新兴投资控股有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>广州市城市建设开发有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种二)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-09-22</t>
+          <t>2033-09-22</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
@@ -7876,7 +7864,7 @@
       </c>
       <c r="AM33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AN33" s="3" t="inlineStr">
@@ -7886,37 +7874,37 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>住宅楼房</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-22</t>
         </is>
       </c>
       <c r="AV33" s="3" t="inlineStr">
@@ -7926,7 +7914,7 @@
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7944,7 +7932,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26泰滨02</t>
+          <t>26HDGJK2</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7954,7 +7942,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>284091.SH</t>
+          <t>246107.SH</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -7963,40 +7951,40 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.52</v>
+        <v>13.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.52</v>
+        <v>13.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.13</v>
+        <v>1.69</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>72.3</v>
+        <v>28.3</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26泰滨01</t>
+          <t>26华电股MTN002</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>4.50Y</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2.0212</t>
+          <t>1.7189</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -8006,12 +7994,12 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>泰州市新滨江开发有限责任公司</t>
+          <t>华电国际电力股份有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 12.94</t>
+          <t>B 54.46</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8021,7 +8009,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-18 16:00</t>
+          <t>09-18 15:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -8035,45 +8023,41 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>3.27</v>
+        <v>3.77</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>2.02%~2.12%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23泰滨06,23泰滨07]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司,中泰证券股份有限公司,华金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD34" s="3" t="inlineStr">
-        <is>
-          <t>泰州港城投资集团有限公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,广发证券股份有限公司,招商证券股份有限公司,兴业证券股份有限公司,中国银河证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -8081,7 +8065,7 @@
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr">
@@ -8091,12 +8075,12 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>泰州市新滨江开发有限责任公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>华电国际电力股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
@@ -8112,7 +8096,7 @@
       </c>
       <c r="AM34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AN34" s="3" t="inlineStr">
@@ -8122,32 +8106,32 @@
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8157,7 +8141,7 @@
       </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW34" s="3" t="inlineStr">
@@ -8180,7 +8164,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26湖产03</t>
+          <t>26泰滨02</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8190,49 +8174,49 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>284117.SH</t>
+          <t>284091.SH</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>7.1</v>
+        <v>7.52</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7.1</v>
+        <v>7.52</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.81</v>
+        <v>2.13</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>40.3</v>
+        <v>72.3</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>24湖产05</t>
+          <t>26泰滨01</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>2.87Y</t>
+          <t>4.50Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.8466</t>
+          <t>2.0212</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -8242,12 +8226,12 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>湖州市产业投资发展集团有限公司</t>
+          <t>泰州市新滨江开发有限责任公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 23.31</t>
+          <t>C- 12.94</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8257,7 +8241,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>09-18 15:00</t>
+          <t>09-18 16:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -8271,37 +8255,45 @@
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>2.86</v>
+        <v>3.27</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X35" s="3"/>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>2.02%~2.12%</t>
+        </is>
+      </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券本金[23湖产K2]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23泰滨06,23泰滨07]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>德邦证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD35" s="3"/>
+          <t>申万宏源证券有限公司,中泰证券股份有限公司,华金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr">
+        <is>
+          <t>泰州港城投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE35" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -8319,7 +8311,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>湖州市产业投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>泰州市新滨江开发有限责任公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8340,7 +8332,7 @@
       </c>
       <c r="AM35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AN35" s="3" t="inlineStr">
@@ -8350,47 +8342,47 @@
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
         <is>
-          <t>2029-09-22</t>
+          <t/>
         </is>
       </c>
       <c r="AV35" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW35" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX35" s="3" t="inlineStr">
@@ -8408,7 +8400,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26皖交02</t>
+          <t>26连工01</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8418,7 +8410,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>246131.SH</t>
+          <t>284016.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -8427,55 +8419,55 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>20.0</v>
+        <v>4.5</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>20.0</v>
+        <v>4.5</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.69</v>
+        <v>2.04</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>28.3</v>
+        <v>63.3</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>24皖交控MTN002</t>
+          <t>24连工03</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>4.44Y</t>
+          <t>212D</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.7081</t>
+          <t>1.7683</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>1.7200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>安徽省交通控股集团有限公司</t>
+          <t>连云港市工业投资集团有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.55</t>
+          <t>C- 13.40</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8495,38 +8487,42 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>3.5</v>
+        <v>2.31</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X36" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>1.97%~2.07%</t>
+        </is>
+      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>江苏省-连云港市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过20亿元(含20亿元)，发行人拟用于偿还上表所列示的公司债券本金[23皖交05]</t>
+          <t>本期公司债券募集资金扣除发行费用后,将全部用于偿还到期债务[26连云工投SCP001]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,招商证券股份有限公司</t>
+          <t>东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
@@ -8547,67 +8543,63 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>安徽省交通控股集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>连云港市工业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-09-21</t>
-        </is>
-      </c>
-      <c r="AK36" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-22</t>
+        </is>
+      </c>
+      <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AN36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>化学原料</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8640,7 +8632,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26柯开02</t>
+          <t>26象集04</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8650,64 +8642,64 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>284077.SH</t>
+          <t>246117.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>5.0</v>
+        <v>7.5</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.70 ~ 2.50</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>41.41</v>
+        <v>79.3</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26柯开01</t>
+          <t>26象屿MTN005</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>2.77Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.6986</t>
+          <t>2.2887</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>绍兴市柯桥区开发经营集团有限公司</t>
+          <t>厦门象屿集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>B 54.04</t>
+          <t>B- 38.95</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8727,19 +8719,23 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X37" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>2.40%~2.50%</t>
+        </is>
+      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8748,17 +8744,17 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金5亿元,拟全部用于偿还到期公司债券本金。[23柯开02]</t>
+          <t>本期债券募集资金拟不超过15.00亿元用于偿还到期公司债券本金或置换偿还公司债券本金的自有资金[23 象屿G4,23 象屿G5]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>兴业证券股份有限公司,华福证券股份有限公司,广发证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,中国银河证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8779,27 +8775,23 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>绍兴市柯桥区开发经营集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>厦门象屿集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2029-09-23</t>
-        </is>
-      </c>
-      <c r="AK37" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-22</t>
+        </is>
+      </c>
+      <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM37" s="3" t="inlineStr">
@@ -8809,25 +8801,37 @@
       </c>
       <c r="AN37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ37" s="3"/>
-      <c r="AR37" s="3"/>
-      <c r="AS37" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr">
+        <is>
+          <t>贸易零售</t>
+        </is>
+      </c>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>其他贸易</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>其他贸易</t>
+        </is>
+      </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8860,7 +8864,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26象集03(取消发行)</t>
+          <t>26万联S3</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8870,81 +8874,89 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>DY246116.SH</t>
+          <t>246096.SH</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>8.0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>8.0</v>
+      </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+          <t>1.10 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>30.02</v>
+      </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>24万联G2</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>1.29Y</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>1.5516</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>万联证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>C- 17.97</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>09-18 15:00</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>24象屿MTN004</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>2.79Y</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>2.0518</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>2.0600/--</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>厦门象屿集团有限公司</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t>B- 38.95</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t>09-18 15:00</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="U38" s="3"/>
+      <c r="U38" s="4" t="n">
+        <v>4.7</v>
+      </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
@@ -8953,7 +8965,7 @@
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>2.19%~2.29%</t>
+          <t>1.54%~1.58%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
@@ -8964,23 +8976,23 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟不超过15.00亿元用于偿还到期公司债券本金或置换偿还公司债券本金的自有资金[23 象屿G4,23 象屿G5]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于补充公司业务等日常生产经营所需流动资金,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出。根据公司财务状况和资金使用需求,公司未来可能调整部分流动资金用于偿还有息债务。发行人承诺,本期债券募集资金中补充流动资金部分,用于融资融券、股票质押、衍生品等资本消耗性业务的规模不超过10%。</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,华福证券股份有限公司,广发证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,中国银河证券股份有限公司,平安证券股份有限公司</t>
+          <t>粤开证券股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8995,7 +9007,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>厦门象屿集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种一)(取消发行)</t>
+          <t>万联证券股份有限公司2026年面向专业投资者公开发行短期公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -9005,17 +9017,13 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2029-09-22</t>
-        </is>
-      </c>
-      <c r="AK38" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-09-22</t>
+        </is>
+      </c>
+      <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM38" s="3" t="inlineStr">
@@ -9030,32 +9038,32 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -9088,7 +9096,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26万联S3</t>
+          <t>26象集03(取消发行)</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -9098,64 +9106,58 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>246096.SH</t>
+          <t>DY246116.SH</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>8.0</v>
-      </c>
+        <v>7.5</v>
+      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>30.02</v>
-      </c>
+          <t>1.50 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>24万联G2</t>
+          <t>24象屿MTN004</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>1.29Y</t>
+          <t>2.79Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.5516</t>
+          <t>2.0518</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0600/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>万联证券股份有限公司</t>
+          <t>厦门象屿集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 17.97</t>
+          <t>B- 38.95</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9178,9 +9180,7 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="U39" s="4" t="n">
-        <v>4.7</v>
-      </c>
+      <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.54%~1.58%</t>
+          <t>2.19%~2.29%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -9200,23 +9200,23 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于补充公司业务等日常生产经营所需流动资金,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出。根据公司财务状况和资金使用需求,公司未来可能调整部分流动资金用于偿还有息债务。发行人承诺,本期债券募集资金中补充流动资金部分,用于融资融券、股票质押、衍生品等资本消耗性业务的规模不超过10%。</t>
+          <t>本期债券募集资金拟不超过15.00亿元用于偿还到期公司债券本金或置换偿还公司债券本金的自有资金[23 象屿G4,23 象屿G5]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>粤开证券股份有限公司</t>
+          <t>兴业证券股份有限公司,华福证券股份有限公司,广发证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,中国银河证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>万联证券股份有限公司2026年面向专业投资者公开发行短期公司债券(第三期)</t>
+          <t>厦门象屿集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9241,13 +9241,17 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2027-09-22</t>
-        </is>
-      </c>
-      <c r="AK39" s="3"/>
+          <t>2029-09-22</t>
+        </is>
+      </c>
+      <c r="AK39" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t/>
         </is>
       </c>
       <c r="AM39" s="3" t="inlineStr">
@@ -9262,32 +9266,32 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -10020,74 +10024,74 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26苏国G3</t>
+          <t>26深燃气SCP005</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>09-18 19:00</t>
+          <t>09-18 18:00</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>246079.SH</t>
+          <t>012682304.IB</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>39.46</v>
+        <v>16.68</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26苏国G1</t>
+          <t>26深燃气SCP002</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2.86Y</t>
+          <t>203D</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.6324</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>1.6900/1.5400</t>
+          <t>1.5200/--</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>苏州国有资本投资集团有限公司</t>
+          <t>深圳市燃气集团股份有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 19.43</t>
+          <t>B 52.26</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10097,7 +10101,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>09-18 15:00</t>
+          <t>09-18 09:00</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -10107,21 +10111,23 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="U43" s="4" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V43" s="3"/>
+        <v>2.22</v>
+      </c>
+      <c r="V43" s="4" t="n">
+        <v>1.15</v>
+      </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -10132,23 +10138,23 @@
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后，拟将不超过15.165亿元用于股权投资；不超过0.835亿元用于偿还有息债务。</t>
+          <t>本期超短期融资券发行规模为人民币10亿元,募集资金将全部用于偿还发行人到期债务融资工具本金。[25深燃气SCP004(科创债)]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,华泰联合证券有限责任公司,中信证券股份有限公司</t>
+          <t>中信银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
@@ -10158,12 +10164,12 @@
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>苏州国有资本投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种二)</t>
+          <t>深圳市燃气集团股份有限公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -10173,13 +10179,13 @@
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2033-09-22</t>
+          <t>2027-06-17</t>
         </is>
       </c>
       <c r="AK43" s="3"/>
       <c r="AL43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AM43" s="3" t="inlineStr">
@@ -10189,33 +10195,37 @@
       </c>
       <c r="AN43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP43" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
@@ -10248,7 +10258,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26深燃气SCP005</t>
+          <t>26龙盛MTN008(科创债)</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -10258,64 +10268,64 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>012682304.IB</t>
+          <t>102683717.IB</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>1.01Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.30 ~ 1.58</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>16.68</v>
+        <v>20.02</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>26深燃气SCP002</t>
+          <t>26龙盛MTN007(科创债)</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>203D</t>
+          <t>312D</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>1.5200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>深圳市燃气集团股份有限公司</t>
+          <t>浙江龙盛集团股份有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>B 52.26</t>
+          <t>B- 35.52</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10335,23 +10345,21 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="U44" s="4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>1.15</v>
-      </c>
+        <v>1.42</v>
+      </c>
+      <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.51%~1.61%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -10362,28 +10370,28 @@
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模为人民币10亿元,募集资金将全部用于偿还发行人到期债务融资工具本金。[25深燃气SCP004(科创债)]</t>
+          <t>本期债务融资工具发行规模为15亿元,拟用于偿还发行人即将到期的债务[26龙盛SCP001(科创债)]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>招商银行股份有限公司,杭州银行股份有限公司,中国民生银行股份有限公司,中国光大银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG44" s="3" t="inlineStr">
@@ -10393,7 +10401,7 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>深圳市燃气集团股份有限公司2026年度第五期超短期融资券</t>
+          <t>浙江龙盛集团股份有限公司2026年度第八期科技创新债券</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10403,25 +10411,25 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2027-06-17</t>
+          <t>2027-09-24</t>
         </is>
       </c>
       <c r="AK44" s="3"/>
       <c r="AL44" s="3" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="AM44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -10429,27 +10437,27 @@
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
@@ -10482,74 +10490,70 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26龙盛MTN008(科创债)</t>
+          <t>26国泰海通CP008</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>09-18 18:00</t>
+          <t>09-18 17:00</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>102683717.IB</t>
+          <t>072610191.IB</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>1.01Y</t>
+          <t>0.64Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>15.0</v>
+        <v>50.0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>1.30 ~ 1.58</t>
-        </is>
-      </c>
+        <v>50.0</v>
+      </c>
+      <c r="G45" s="3"/>
       <c r="H45" s="4" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>20.02</v>
+        <v>30.38</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26龙盛MTN007(科创债)</t>
+          <t>26国泰海通CP005</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>312D</t>
+          <t>252D</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.5079</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/--</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>浙江龙盛集团股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>B- 35.52</t>
+          <t>A- 68.49</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10572,18 +10576,16 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="U45" s="4" t="n">
-        <v>1.42</v>
-      </c>
+      <c r="U45" s="3"/>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.61%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -10594,28 +10596,24 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
-        </is>
-      </c>
-      <c r="AB45" s="3" t="inlineStr">
-        <is>
-          <t>本期债务融资工具发行规模为15亿元,拟用于偿还发行人即将到期的债务[26龙盛SCP001(科创债)]</t>
-        </is>
-      </c>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="AB45" s="3"/>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,杭州银行股份有限公司,中国民生银行股份有限公司,中国光大银行股份有限公司,中信银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG45" s="3" t="inlineStr">
@@ -10625,7 +10623,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>浙江龙盛集团股份有限公司2026年度第八期科技创新债券</t>
+          <t>国泰海通证券股份有限公司2026年度第八期短期融资券</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10635,7 +10633,7 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2027-09-24</t>
+          <t>2027-05-14</t>
         </is>
       </c>
       <c r="AK45" s="3"/>
@@ -10646,7 +10644,7 @@
       </c>
       <c r="AM45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AN45" s="3" t="inlineStr">
@@ -10656,32 +10654,32 @@
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
@@ -10714,7 +10712,7 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP008</t>
+          <t>26广发银行债03</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10724,60 +10722,60 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>072610191.IB</t>
+          <t>212680053.IB</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>0.64Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="4" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>30.38</v>
+        <v>30.41</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP005</t>
+          <t>26广发银行债02</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>252D</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.5079</t>
+          <t>1.5728</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>1.5100/--</t>
+          <t>1.5800/1.5750</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>广发银行股份有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>A- 68.49</t>
+          <t>S 92.88</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10787,7 +10785,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>09-18 09:00</t>
+          <t>09-18 09:30</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -10804,12 +10802,12 @@
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
@@ -10820,24 +10818,24 @@
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="AB46" s="3"/>
-      <c r="AC46" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通证券股份有限公司</t>
-        </is>
-      </c>
+          <t>广东省-广州市</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC46" s="3"/>
       <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG46" s="3" t="inlineStr">
@@ -10847,7 +10845,7 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司2026年度第八期短期融资券</t>
+          <t>广发银行股份有限公司2026年金融债券(第三期)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10857,7 +10855,7 @@
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2027-05-14</t>
+          <t>2029-09-21</t>
         </is>
       </c>
       <c r="AK46" s="3"/>
@@ -10868,14 +10866,14 @@
       </c>
       <c r="AM46" s="3" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>金融</t>
@@ -10883,27 +10881,27 @@
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
@@ -10936,70 +10934,74 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26广发银行债03</t>
+          <t>26中建六局MTN002(可持续挂钩)</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>09-18 17:00</t>
+          <t>09-18 18:00</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>212680053.IB</t>
+          <t>102683721.IB</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>100.0</v>
+        <v>7.0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="G47" s="3"/>
+        <v>7.0</v>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.10</t>
+        </is>
+      </c>
       <c r="H47" s="4" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>30.41</v>
+        <v>48.41</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26广发银行债02</t>
+          <t>26中建六局MTN001(可持续挂钩)</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>2.94Y+N</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.5728</t>
+          <t>1.7432</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>1.5800/1.5750</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司</t>
+          <t>中国建筑第六工程局有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>S 92.88</t>
+          <t>B- 41.67</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -11009,12 +11011,12 @@
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>09-18 09:30</t>
+          <t>09-18 09:00</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="T47" s="3" t="inlineStr">
@@ -11022,16 +11024,18 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="U47" s="3"/>
+      <c r="U47" s="4" t="n">
+        <v>2.57</v>
+      </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
@@ -11039,22 +11043,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z47" s="3"/>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC47" s="3"/>
+          <t>本期发行金额为人民币7亿元，募集资金拟用于偿还发行人本部存量债务。【23 中建六局MTN002(科创票据)】</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>中国银行股份有限公司,国泰海通证券股份有限公司</t>
+        </is>
+      </c>
       <c r="AD47" s="3"/>
       <c r="AE47" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF47" s="3" t="inlineStr">
@@ -11069,7 +11081,7 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司2026年金融债券(第三期)</t>
+          <t>中国建筑第六工程局有限公司2026年度第二期中期票据(可持续挂钩)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -11100,32 +11112,32 @@
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP47" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ47" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>房屋建筑</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>其他房建</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
@@ -11140,12 +11152,12 @@
       </c>
       <c r="AW47" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX47" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY47" s="3" t="inlineStr">
@@ -11153,79 +11165,77 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="AZ47" s="3"/>
+      <c r="AZ47" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26中建六局MTN002(可持续挂钩)</t>
+          <t>26国信证券CP008</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>09-18 18:00</t>
+          <t>09-18 17:00</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>102683721.IB</t>
+          <t>072610190.IB</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.37Y</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>7.0</v>
+        <v>20.0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.10</t>
-        </is>
-      </c>
+        <v>20.0</v>
+      </c>
+      <c r="G48" s="3"/>
       <c r="H48" s="4" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>48.41</v>
+        <v>29.41</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>26中建六局MTN001(可持续挂钩)</t>
+          <t>26国信证券CP001</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2.94Y+N</t>
+          <t>112D</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.7432</t>
+          <t>1.4526</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5000/--</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>中国建筑第六工程局有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>B- 41.67</t>
+          <t>B+ 58.75</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11248,18 +11258,16 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="U48" s="4" t="n">
-        <v>2.57</v>
-      </c>
+      <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.44%~1.48%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
@@ -11267,35 +11275,27 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z48" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
-        </is>
-      </c>
-      <c r="AB48" s="3" t="inlineStr">
-        <is>
-          <t>本期发行金额为人民币7亿元，募集资金拟用于偿还发行人本部存量债务。【23 中建六局MTN002(科创票据)】</t>
-        </is>
-      </c>
+          <t>广东省-深圳市</t>
+        </is>
+      </c>
+      <c r="AB48" s="3"/>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,国泰海通证券股份有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF48" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG48" s="3" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>中国建筑第六工程局有限公司2026年度第二期中期票据(可持续挂钩)</t>
+          <t>国信证券股份有限公司2026年度第八期短期融资券</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2029-09-21</t>
+          <t>2027-02-02</t>
         </is>
       </c>
       <c r="AK48" s="3"/>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="AM48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AN48" s="3" t="inlineStr">
@@ -11336,32 +11336,32 @@
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP48" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ48" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">
@@ -11376,12 +11376,12 @@
       </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX48" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY48" s="3" t="inlineStr">
@@ -11389,77 +11389,79 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="AZ48" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ48" s="3"/>
     </row>
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>26国信证券CP008</t>
+          <t>26中航租赁SCP007</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>09-18 17:00</t>
+          <t>09-18 18:00</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>072610190.IB</t>
+          <t>012682306.IB</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>0.37Y</t>
+          <t>0.57Y</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="G49" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>1.38 ~ 1.58</t>
+        </is>
+      </c>
       <c r="H49" s="4" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>29.41</v>
+        <v>34.38</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>26国信证券CP001</t>
+          <t>26中航租赁SCP006</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>112D</t>
+          <t>182D</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>1.4526</t>
+          <t>1.5800</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>1.5000/--</t>
+          <t>1.5900/--</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>中航国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>B+ 58.75</t>
+          <t>C- 18.28</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -11474,7 +11476,7 @@
       </c>
       <c r="S49" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="T49" s="3" t="inlineStr">
@@ -11482,16 +11484,20 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="U49" s="3"/>
-      <c r="V49" s="3"/>
+      <c r="U49" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V49" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X49" s="3" t="inlineStr">
         <is>
-          <t>1.44%~1.48%</t>
+          <t>1.54%~1.58%</t>
         </is>
       </c>
       <c r="Y49" s="3" t="inlineStr">
@@ -11502,24 +11508,28 @@
       <c r="Z49" s="3"/>
       <c r="AA49" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
-        </is>
-      </c>
-      <c r="AB49" s="3"/>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>本期超短期融资券发行金额5亿元，本次超短期融资券募集资金拟全部用于偿还发行人即将到期的债务融资工具。[26中航租赁SCP001]</t>
+        </is>
+      </c>
       <c r="AC49" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>南京银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD49" s="3"/>
       <c r="AE49" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF49" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG49" s="3" t="inlineStr">
@@ -11529,7 +11539,7 @@
       </c>
       <c r="AH49" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司2026年度第八期短期融资券</t>
+          <t>中航国际融资租赁有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI49" s="3" t="inlineStr">
@@ -11539,7 +11549,7 @@
       </c>
       <c r="AJ49" s="3" t="inlineStr">
         <is>
-          <t>2027-02-02</t>
+          <t>2027-04-16</t>
         </is>
       </c>
       <c r="AK49" s="3"/>
@@ -11550,14 +11560,14 @@
       </c>
       <c r="AM49" s="3" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>金融</t>
@@ -11565,7 +11575,7 @@
       </c>
       <c r="AP49" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ49" s="3" t="inlineStr">
@@ -11575,17 +11585,17 @@
       </c>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT49" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU49" s="3" t="inlineStr">
@@ -11613,79 +11623,81 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="AZ49" s="3"/>
+      <c r="AZ49" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="50" customHeight="true" ht="18.0">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>26中航租赁SCP007</t>
+          <t>26江汉01</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>09-18 18:00</t>
+          <t>09-18 19:00</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>012682306.IB</t>
+          <t>284078.SH</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>0.57Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>1.38 ~ 1.58</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>34.38</v>
+        <v>46.41</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>26中航租赁SCP006</t>
+          <t>25江汉01</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>182D</t>
+          <t>1.33Y</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1.5800</t>
+          <t>1.7647</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>1.5900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>中航国际融资租赁有限公司</t>
+          <t>武汉金融街集团有限公司</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>C- 18.28</t>
+          <t>C- 18.75</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -11695,7 +11707,7 @@
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>09-18 09:00</t>
+          <t>09-18 15:00</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
@@ -11709,19 +11721,17 @@
         </is>
       </c>
       <c r="U50" s="4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>3.0</v>
-      </c>
+        <v>8.07</v>
+      </c>
+      <c r="V50" s="3"/>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X50" s="3" t="inlineStr">
         <is>
-          <t>1.54%~1.58%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y50" s="3" t="inlineStr">
@@ -11732,54 +11742,54 @@
       <c r="Z50" s="3"/>
       <c r="AA50" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB50" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额5亿元，本次超短期融资券募集资金拟全部用于偿还发行人即将到期的债务融资工具。[26中航租赁SCP001]</t>
+          <t>本期债券发行规模为不超过3亿元(含3亿元),本期公司债券募集资金扣除发行费用后,拟用于置换已到期公司债券本金。[23江汉01]</t>
         </is>
       </c>
       <c r="AC50" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,渤海银行股份有限公司</t>
+          <t>长江证券股份有限公司</t>
         </is>
       </c>
       <c r="AD50" s="3"/>
       <c r="AE50" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF50" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG50" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH50" s="3" t="inlineStr">
         <is>
-          <t>中航国际融资租赁有限公司2026年度第七期超短期融资券</t>
+          <t>武汉金融街集团有限公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="AI50" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ50" s="3" t="inlineStr">
         <is>
-          <t>2027-04-16</t>
+          <t>2029-09-21</t>
         </is>
       </c>
       <c r="AK50" s="3"/>
       <c r="AL50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM50" s="3" t="inlineStr">
@@ -11794,32 +11804,32 @@
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP50" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ50" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT50" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU50" s="3" t="inlineStr">
@@ -11847,24 +11857,22 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="AZ50" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ50" s="3"/>
     </row>
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>26江汉01</t>
+          <t>26阜阳投资PPN001</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>09-18 19:00</t>
+          <t>09-18 18:00</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>284078.SH</t>
+          <t>032680530.IB</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -11873,40 +11881,40 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>3.0</v>
+        <v>2.9</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>3.0</v>
+        <v>2.9</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.10</t>
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>46.41</v>
+        <v>49.41</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>25江汉01</t>
+          <t>25阜投04</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>1.33Y</t>
+          <t>2.25Y</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>1.7647</t>
+          <t>1.6714</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
@@ -11916,12 +11924,12 @@
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>武汉金融街集团有限公司</t>
+          <t>阜阳投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>C- 18.75</t>
+          <t>B- 44.67</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -11931,12 +11939,12 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>09-18 15:00</t>
+          <t>09-18 09:00</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="T51" s="3" t="inlineStr">
@@ -11945,44 +11953,46 @@
         </is>
       </c>
       <c r="U51" s="4" t="n">
-        <v>8.07</v>
-      </c>
-      <c r="V51" s="3"/>
+        <v>3.6793</v>
+      </c>
+      <c r="V51" s="4" t="n">
+        <v>1.6</v>
+      </c>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X51" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y51" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z51" s="3"/>
       <c r="AA51" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>安徽省-阜阳市</t>
         </is>
       </c>
       <c r="AB51" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过3亿元(含3亿元),本期公司债券募集资金扣除发行费用后,拟用于置换已到期公司债券本金。[23江汉01]</t>
+          <t>本次定向债务融资工具注册规模12.15亿元，首期发行规模2.90亿元，募集资金全部用于偿还发行人存量债务融资工具本金[23阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004,24阜阳投资MTN001,24阜阳投资MTN002]</t>
         </is>
       </c>
       <c r="AC51" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司</t>
+          <t>徽商银行股份有限公司,交通银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD51" s="3"/>
       <c r="AE51" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF51" s="3" t="inlineStr">
@@ -11992,12 +12002,12 @@
       </c>
       <c r="AG51" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH51" s="3" t="inlineStr">
         <is>
-          <t>武汉金融街集团有限公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>阜阳投资发展集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI51" s="3" t="inlineStr">
@@ -12013,7 +12023,7 @@
       <c r="AK51" s="3"/>
       <c r="AL51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AM51" s="3" t="inlineStr">
@@ -12033,22 +12043,22 @@
       </c>
       <c r="AP51" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ51" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT51" s="3" t="inlineStr">
@@ -12081,12 +12091,14 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="AZ51" s="3"/>
+      <c r="AZ51" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="52" customHeight="true" ht="18.0">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>26阜阳投资PPN001</t>
+          <t>26广州控股MTN006A</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -12096,64 +12108,64 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>032680530.IB</t>
+          <t>102683728.IB</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>2.9</v>
+        <v>5.0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2.9</v>
+        <v>5.0</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.10</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>49.41</v>
+        <v>50.41</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>25阜投04</t>
+          <t>26广州控股MTN002A</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2.25Y</t>
+          <t>2.93Y+N</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1.6714</t>
+          <t>1.7925</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7900/--</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>阜阳投资发展集团有限公司</t>
+          <t>广州开发区控股集团有限公司</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>B- 44.67</t>
+          <t>C+ 33.33</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -12168,7 +12180,7 @@
       </c>
       <c r="S52" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="T52" s="3" t="inlineStr">
@@ -12177,46 +12189,50 @@
         </is>
       </c>
       <c r="U52" s="4" t="n">
-        <v>3.6793</v>
+        <v>5.36</v>
       </c>
       <c r="V52" s="4" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X52" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z52" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA52" s="3" t="inlineStr">
         <is>
-          <t>安徽省-阜阳市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB52" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具注册规模12.15亿元，首期发行规模2.90亿元，募集资金全部用于偿还发行人存量债务融资工具本金[23阜阳投资MTN002,23阜阳投资PPN002,23阜阳投资PPN004,24阜阳投资MTN001,24阜阳投资MTN002]</t>
+          <t>本期中期票据发行规模不超过10亿元,用于偿还发行人本部及下属子公司的有息债务。</t>
         </is>
       </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司,交通银行股份有限公司,兴业银行股份有限公司</t>
+          <t>华夏银行股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD52" s="3"/>
       <c r="AE52" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF52" s="3" t="inlineStr">
@@ -12231,12 +12247,12 @@
       </c>
       <c r="AH52" s="3" t="inlineStr">
         <is>
-          <t>阜阳投资发展集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>广州开发区控股集团有限公司2026年度第六期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI52" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ52" s="3" t="inlineStr">
@@ -12262,12 +12278,12 @@
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP52" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ52" s="3" t="inlineStr">
@@ -12277,17 +12293,17 @@
       </c>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT52" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU52" s="3" t="inlineStr">
@@ -12302,12 +12318,12 @@
       </c>
       <c r="AW52" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX52" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY52" s="3" t="inlineStr">
@@ -12322,7 +12338,7 @@
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26广州控股MTN006A</t>
+          <t>26广州控股MTN006B</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -12332,12 +12348,12 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>102683728.IB</t>
+          <t>102683729.IB</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
@@ -12348,38 +12364,38 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>50.41</v>
+        <v>57.3</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>26广州控股MTN002A</t>
+          <t>26广州控股MTN002B</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>2.93Y+N</t>
+          <t>4.93Y+N</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>1.7925</t>
+          <t>2.0255</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>1.7900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
@@ -12404,7 +12420,7 @@
       </c>
       <c r="S53" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="T53" s="3" t="inlineStr">
@@ -12413,10 +12429,10 @@
         </is>
       </c>
       <c r="U53" s="4" t="n">
-        <v>5.36</v>
+        <v>3.98</v>
       </c>
       <c r="V53" s="4" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="W53" s="3" t="inlineStr">
         <is>
@@ -12425,7 +12441,7 @@
       </c>
       <c r="X53" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y53" s="3" t="inlineStr">
@@ -12471,7 +12487,7 @@
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>广州开发区控股集团有限公司2026年度第六期中期票据(品种一)</t>
+          <t>广州开发区控股集团有限公司2026年度第六期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
@@ -12481,10 +12497,14 @@
       </c>
       <c r="AJ53" s="3" t="inlineStr">
         <is>
-          <t>2029-09-21</t>
-        </is>
-      </c>
-      <c r="AK53" s="3"/>
+          <t>2031-09-21</t>
+        </is>
+      </c>
+      <c r="AK53" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL53" s="3" t="inlineStr">
         <is>
           <t>2026-09-22</t>
@@ -12562,7 +12582,7 @@
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26广州控股MTN006B</t>
+          <t>26天街集团MTN001</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -12572,64 +12592,64 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>102683729.IB</t>
+          <t>102683726.IB</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>57.3</v>
+        <v>41.41</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>26广州控股MTN002B</t>
+          <t>23天街集团MTN001</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>4.93Y+N</t>
+          <t>39D</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>2.0255</t>
+          <t>1.5521</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5800/--</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>广州开发区控股集团有限公司</t>
+          <t>北京天街集团有限公司</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.33</t>
+          <t>C 26.88</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12639,12 +12659,12 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>09-18 09:00</t>
+          <t>09-18 15:00</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="T54" s="3" t="inlineStr">
@@ -12653,44 +12673,38 @@
         </is>
       </c>
       <c r="U54" s="4" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>1.58</v>
-      </c>
+        <v>5.9267</v>
+      </c>
+      <c r="V54" s="3"/>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X54" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y54" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z54" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z54" s="3"/>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>北京市-东城区</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模不超过10亿元,用于偿还发行人本部及下属子公司的有息债务。</t>
+          <t>发行人本次债券注册规模25亿元,本期债务融资工具基础发行规模0亿元,发行金额上限15亿元,用于偿还存量债务融资工具。[23天街集团MTN001]</t>
         </is>
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>华夏银行股份有限公司,广发证券股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD54" s="3"/>
@@ -12711,7 +12725,7 @@
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>广州开发区控股集团有限公司2026年度第六期中期票据(品种二)</t>
+          <t>北京天街集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
@@ -12721,14 +12735,10 @@
       </c>
       <c r="AJ54" s="3" t="inlineStr">
         <is>
-          <t>2031-09-21</t>
-        </is>
-      </c>
-      <c r="AK54" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-21</t>
+        </is>
+      </c>
+      <c r="AK54" s="3"/>
       <c r="AL54" s="3" t="inlineStr">
         <is>
           <t>2026-09-22</t>
@@ -12746,32 +12756,32 @@
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP54" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ54" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT54" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU54" s="3" t="inlineStr">
@@ -12786,12 +12796,12 @@
       </c>
       <c r="AW54" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX54" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY54" s="3" t="inlineStr">
@@ -12799,14 +12809,12 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="AZ54" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ54" s="3"/>
     </row>
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>26天街集团MTN001</t>
+          <t>26南京医药SCP012</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -12816,64 +12824,64 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>102683726.IB</t>
+          <t>012682302.IB</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>1.68</v>
+        <v>1.39</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>41.41</v>
+        <v>18.68</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>23天街集团MTN001</t>
+          <t>26南京医药SCP011</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>39D</t>
+          <t>248D</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>1.5521</t>
+          <t>1.5335</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>1.5800/--</t>
+          <t>1.5600/--</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>北京天街集团有限公司</t>
+          <t>南京医药集团股份有限公司</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>C 26.88</t>
+          <t>B- 40.05</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -12883,7 +12891,7 @@
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>09-18 15:00</t>
+          <t>09-18 09:00</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
@@ -12893,21 +12901,21 @@
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="U55" s="4" t="n">
-        <v>5.9267</v>
+        <v>2.38</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X55" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.55%~1.59%</t>
         </is>
       </c>
       <c r="Y55" s="3" t="inlineStr">
@@ -12918,23 +12926,23 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>北京市-东城区</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB55" s="3" t="inlineStr">
         <is>
-          <t>发行人本次债券注册规模25亿元,本期债务融资工具基础发行规模0亿元,发行金额上限15亿元,用于偿还存量债务融资工具。[23天街集团MTN001]</t>
+          <t>本期超短期融资券发行金额5亿元,本期发行的募集资金扣除发行费用后用于发行人本级及下属子公司补充流动资金。</t>
         </is>
       </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF55" s="3" t="inlineStr">
@@ -12949,7 +12957,7 @@
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>北京天街集团有限公司2026年度第一期中期票据</t>
+          <t>南京医药集团股份有限公司2026年度第十二期超短期融资券</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
@@ -12959,13 +12967,13 @@
       </c>
       <c r="AJ55" s="3" t="inlineStr">
         <is>
-          <t>2029-09-21</t>
+          <t>2027-06-17</t>
         </is>
       </c>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AM55" s="3" t="inlineStr">
@@ -12975,37 +12983,37 @@
       </c>
       <c r="AN55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP55" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ55" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>医药流通</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>医药流通</t>
         </is>
       </c>
       <c r="AT55" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>医药商业</t>
         </is>
       </c>
       <c r="AU55" s="3" t="inlineStr">
@@ -13038,7 +13046,7 @@
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>26南京医药SCP012</t>
+          <t>26港口Y3</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -13048,64 +13056,64 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>012682302.IB</t>
+          <t>246115.SH</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>2+N</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>18.68</v>
+        <v>37.43</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>26南京医药SCP011</t>
+          <t>26港口Y2</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>248D</t>
+          <t>1.95Y+N</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1.5335</t>
+          <t>1.6424</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>1.5600/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>南京医药集团股份有限公司</t>
+          <t>福建省港口集团有限责任公司</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>B- 40.05</t>
+          <t>B- 39.39</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -13115,7 +13123,7 @@
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>09-18 09:00</t>
+          <t>09-18 15:00</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr">
@@ -13125,48 +13133,44 @@
       </c>
       <c r="T56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="U56" s="4" t="n">
-        <v>2.38</v>
+        <v>3.23</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X56" s="3" t="inlineStr">
-        <is>
-          <t>1.55%~1.59%</t>
-        </is>
-      </c>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X56" s="3"/>
       <c r="Y56" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额5亿元,本期发行的募集资金扣除发行费用后用于发行人本级及下属子公司补充流动资金。</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还公司债务。</t>
         </is>
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,华福证券股份有限公司,兴业证券股份有限公司</t>
         </is>
       </c>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF56" s="3" t="inlineStr">
@@ -13176,12 +13180,12 @@
       </c>
       <c r="AG56" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>南京医药集团股份有限公司2026年度第十二期超短期融资券</t>
+          <t>福建省港口集团有限责任公司2026年面向专业投资者公开发行可续期公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
@@ -13191,13 +13195,13 @@
       </c>
       <c r="AJ56" s="3" t="inlineStr">
         <is>
-          <t>2027-06-17</t>
+          <t>2028-09-22</t>
         </is>
       </c>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t/>
         </is>
       </c>
       <c r="AM56" s="3" t="inlineStr">
@@ -13207,7 +13211,7 @@
       </c>
       <c r="AN56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AO56" s="3" t="inlineStr">
@@ -13217,27 +13221,27 @@
       </c>
       <c r="AP56" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ56" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>医药流通</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
         <is>
-          <t>医药流通</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT56" s="3" t="inlineStr">
         <is>
-          <t>医药商业</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU56" s="3" t="inlineStr">
@@ -13252,12 +13256,12 @@
       </c>
       <c r="AW56" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX56" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY56" s="3" t="inlineStr">
@@ -13270,74 +13274,74 @@
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26广城08</t>
+          <t>26建行永续债02BC</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>09-18 19:00</t>
+          <t>09-18 18:00</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>246100.SH</t>
+          <t>242680046.IB</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>10.5</v>
+        <v>150.0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>21.0</v>
+        <v>400.0</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>41.46</v>
+        <v>42.3</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>26广城06</t>
+          <t>26建行永续债01BC</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>4.86Y+2.00Y</t>
+          <t>4.75Y+N</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>2.0326</t>
+          <t>1.8191</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8200/1.8100</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>广州市城市建设开发有限公司</t>
+          <t>中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>B- 44.31</t>
+          <t>S- 87.46</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13347,12 +13351,12 @@
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>09-18 16:00</t>
+          <t>09-18 09:00</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="T57" s="3" t="inlineStr">
@@ -13360,16 +13364,18 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="U57" s="4" t="n">
-        <v>2.73</v>
-      </c>
+      <c r="U57" s="3"/>
       <c r="V57" s="3"/>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X57" s="3"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
       <c r="Y57" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -13382,42 +13388,38 @@
       </c>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过21亿元(含21亿元),募集资金扣除发行费用后,拟全部用于偿还到期公司债券[21穗建05,23穗建07]</t>
+          <t>本期债券募集资金将依据适用法律和主管部门的批准用于补充发行人其他一级资本。</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD57" s="3" t="inlineStr">
-        <is>
-          <t>广州越秀集团股份有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司,中国工商银行股份有限公司,中国邮政储蓄银行股份有限公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,中国银河证券股份有限公司,招商证券股份有限公司,兴业证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD57" s="3"/>
       <c r="AE57" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行次级债券</t>
         </is>
       </c>
       <c r="AF57" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG57" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>广州市城市建设开发有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种二)</t>
+          <t>中国建设银行股份有限公司2026年无固定期限资本债券(第二期)(债券通)</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
@@ -13427,18 +13429,18 @@
       </c>
       <c r="AJ57" s="3" t="inlineStr">
         <is>
-          <t>2033-09-22</t>
+          <t>2031-09-22</t>
         </is>
       </c>
       <c r="AK57" s="3"/>
       <c r="AL57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AN57" s="3" t="inlineStr">
@@ -13448,52 +13450,52 @@
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP57" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ57" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>住宅楼房</t>
+          <t>国有银行</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU57" s="3" t="inlineStr">
         <is>
-          <t>2031-09-22</t>
+          <t/>
         </is>
       </c>
       <c r="AV57" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW57" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX57" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>其他一级资本工具</t>
         </is>
       </c>
       <c r="AY57" s="3" t="inlineStr">
@@ -13506,59 +13508,59 @@
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26港口Y3</t>
+          <t>26鲁铁06</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>09-18 18:00</t>
+          <t>09-18 19:00</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>246115.SH</t>
+          <t>284105.SH</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>2+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>37.43</v>
+        <v>36.3</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>26港口Y2</t>
+          <t>26鲁铁04</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>1.95Y+N</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1.6424</t>
+          <t>1.8848</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -13568,12 +13570,12 @@
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>福建省港口集团有限责任公司</t>
+          <t>山东铁路投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>B- 39.39</t>
+          <t>C- 21.51</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13593,16 +13595,16 @@
       </c>
       <c r="T58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="U58" s="4" t="n">
-        <v>3.23</v>
+        <v>5.12</v>
       </c>
       <c r="V58" s="3"/>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X58" s="3"/>
@@ -13614,17 +13616,17 @@
       <c r="Z58" s="3"/>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="AB58" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还公司债务。</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于全资子公司山东铁投能源投资集团有限公司增资,预计出资时间为2026年底前;剩余部分将用于补充公司日常生产经营所需流动资金,包括但不限于购置高铁项目配套设施等</t>
         </is>
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,华福证券股份有限公司,兴业证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,中泰证券股份有限公司,东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD58" s="3"/>
@@ -13645,70 +13647,74 @@
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>福建省港口集团有限责任公司2026年面向专业投资者公开发行可续期公司债券(第三期)</t>
+          <t>山东铁路投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2028-09-22</t>
-        </is>
-      </c>
-      <c r="AK58" s="3"/>
+          <t>2031-09-21</t>
+        </is>
+      </c>
+      <c r="AK58" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL58" s="3" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ58" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>铁路运输</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM58" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AO58" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP58" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ58" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR58" s="3" t="inlineStr">
-        <is>
-          <t>港口</t>
-        </is>
-      </c>
-      <c r="AS58" s="3" t="inlineStr">
-        <is>
-          <t>港口</t>
-        </is>
-      </c>
-      <c r="AT58" s="3" t="inlineStr">
-        <is>
-          <t>港口</t>
-        </is>
-      </c>
-      <c r="AU58" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV58" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -13716,12 +13722,12 @@
       </c>
       <c r="AW58" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX58" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY58" s="3" t="inlineStr">
@@ -13734,7 +13740,7 @@
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26建行永续债02BC</t>
+          <t>26金隅冀东CP001</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -13744,64 +13750,64 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>242680046.IB</t>
+          <t>042680321.IB</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>150.0</v>
+        <v>10.0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>400.0</v>
+        <v>10.0</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>1.45 ~ 1.70</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>42.3</v>
+        <v>32.02</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>26建行永续债01BC</t>
+          <t>24冀东02</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>4.75Y+N</t>
+          <t>1.01Y+2.00Y</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>1.8191</t>
+          <t>1.5516</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>1.8200/1.8100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司</t>
+          <t>金隅冀东水泥集团股份有限公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>S- 87.46</t>
+          <t>B 53.40</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13816,24 +13822,26 @@
       </c>
       <c r="S59" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="T59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="U59" s="3"/>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="U59" s="4" t="n">
+        <v>2.8</v>
+      </c>
       <c r="V59" s="3"/>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X59" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.57%~1.61%</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
@@ -13841,35 +13849,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z59" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z59" s="3"/>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将依据适用法律和主管部门的批准用于补充发行人其他一级资本。</t>
+          <t>本期发行金隅冀东水泥集团股份有限公司2026年度第一期短期融资券，发行金额10亿元，募集资金拟用于偿还发行人到期兑付的公司债本金和金融机构借款，拟偿还的有息债务中不涉及政府性债务。</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国工商银行股份有限公司,中国邮政储蓄银行股份有限公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,中国银河证券股份有限公司,招商证券股份有限公司,兴业证券股份有限公司</t>
+          <t>招商银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
       <c r="AE59" s="3" t="inlineStr">
         <is>
-          <t>商业银行次级债券</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF59" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG59" s="3" t="inlineStr">
@@ -13879,7 +13883,7 @@
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司2026年无固定期限资本债券(第二期)(债券通)</t>
+          <t>金隅冀东水泥集团股份有限公司2026年度第一期短期融资券</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
@@ -13889,53 +13893,53 @@
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
-          <t>2031-09-22</t>
+          <t>2027-09-21</t>
         </is>
       </c>
       <c r="AK59" s="3"/>
       <c r="AL59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AM59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AN59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>国有银行</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
@@ -13950,12 +13954,12 @@
       </c>
       <c r="AW59" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX59" s="3" t="inlineStr">
         <is>
-          <t>其他一级资本工具</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY59" s="3" t="inlineStr">
@@ -13968,7 +13972,7 @@
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26苏国G2</t>
+          <t>26苏国G3</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -13978,34 +13982,34 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>246075.SH</t>
+          <t>246079.SH</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
         <v>8.0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>11.0</v>
+        <v>5.0</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>28.41</v>
+        <v>39.46</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
@@ -14025,7 +14029,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>1.6900/1.5400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
@@ -14059,7 +14063,7 @@
         </is>
       </c>
       <c r="U60" s="4" t="n">
-        <v>4.93</v>
+        <v>4.25</v>
       </c>
       <c r="V60" s="3"/>
       <c r="W60" s="3" t="inlineStr">
@@ -14069,7 +14073,7 @@
       </c>
       <c r="X60" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
@@ -14111,7 +14115,7 @@
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>苏州国有资本投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种一)</t>
+          <t>苏州国有资本投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
@@ -14121,14 +14125,10 @@
       </c>
       <c r="AJ60" s="3" t="inlineStr">
         <is>
-          <t>2029-09-22</t>
-        </is>
-      </c>
-      <c r="AK60" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2033-09-22</t>
+        </is>
+      </c>
+      <c r="AK60" s="3"/>
       <c r="AL60" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -14200,7 +14200,7 @@
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26鲁铁06</t>
+          <t>26横琴05</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -14210,49 +14210,49 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>284105.SH</t>
+          <t>284069.SH</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.20 ~ 2.10</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>36.3</v>
+        <v>52.41</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>26鲁铁04</t>
+          <t>24横琴02</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>3.10Y</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>1.8848</t>
+          <t>1.8525</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -14262,12 +14262,12 @@
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>山东铁路投资控股集团有限公司</t>
+          <t>珠海大横琴集团有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>C- 21.51</t>
+          <t>B- 46.75</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -14287,16 +14287,16 @@
       </c>
       <c r="T61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="U61" s="4" t="n">
-        <v>5.12</v>
+        <v>3.51</v>
       </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X61" s="3"/>
@@ -14308,17 +14308,17 @@
       <c r="Z61" s="3"/>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于全资子公司山东铁投能源投资集团有限公司增资,预计出资时间为2026年底前;剩余部分将用于补充公司日常生产经营所需流动资金,包括但不限于购置高铁项目配套设施等</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务。</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,中泰证券股份有限公司,东方证券股份有限公司</t>
+          <t>平安证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD61" s="3"/>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>山东铁路投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)</t>
+          <t>珠海大横琴集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
@@ -14349,17 +14349,17 @@
       </c>
       <c r="AJ61" s="3" t="inlineStr">
         <is>
-          <t>2031-09-21</t>
+          <t>2029-09-22</t>
         </is>
       </c>
       <c r="AK61" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM61" s="3" t="inlineStr">
@@ -14369,17 +14369,17 @@
       </c>
       <c r="AN61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP61" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ61" s="3" t="inlineStr">
@@ -14389,17 +14389,17 @@
       </c>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT61" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU61" s="3" t="inlineStr">
@@ -14432,59 +14432,59 @@
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26金隅冀东CP001</t>
+          <t>26苏国G2</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>09-18 18:00</t>
+          <t>09-18 19:00</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>042680321.IB</t>
+          <t>246075.SH</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.45 ~ 1.70</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
         <v>1.55</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>32.02</v>
+        <v>28.41</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>24冀东02</t>
+          <t>26苏国G1</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>1.01Y+2.00Y</t>
+          <t>2.86Y</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.5516</t>
+          <t>1.6324</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -14494,12 +14494,12 @@
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>金隅冀东水泥集团股份有限公司</t>
+          <t>苏州国有资本投资集团有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>B 53.40</t>
+          <t>C- 19.43</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>09-18 09:00</t>
+          <t>09-18 15:00</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr">
@@ -14519,21 +14519,21 @@
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="U62" s="4" t="n">
-        <v>2.8</v>
+        <v>4.93</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.61%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y62" s="3" t="inlineStr">
@@ -14544,23 +14544,23 @@
       <c r="Z62" s="3"/>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>河北省-唐山市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>本期发行金隅冀东水泥集团股份有限公司2026年度第一期短期融资券，发行金额10亿元，募集资金拟用于偿还发行人到期兑付的公司债本金和金融机构借款，拟偿还的有息债务中不涉及政府性债务。</t>
+          <t>本期公司债券募集资金扣除发行费用后，拟将不超过15.165亿元用于股权投资；不超过0.835亿元用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,交通银行股份有限公司</t>
+          <t>东吴证券股份有限公司,华泰联合证券有限责任公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD62" s="3"/>
       <c r="AE62" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF62" s="3" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="AG62" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>金隅冀东水泥集团股份有限公司2026年度第一期短期融资券</t>
+          <t>苏州国有资本投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
@@ -14585,53 +14585,53 @@
       </c>
       <c r="AJ62" s="3" t="inlineStr">
         <is>
-          <t>2027-09-21</t>
-        </is>
-      </c>
-      <c r="AK62" s="3"/>
+          <t>2029-09-22</t>
+        </is>
+      </c>
+      <c r="AK62" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL62" s="3" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AM62" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AN62" s="3" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="AM62" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AN62" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP62" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP62" s="3"/>
       <c r="AQ62" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT62" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU62" s="3" t="inlineStr">
